--- a/labs/03-copilot-studio/04-ui-update/03-evaluations/lab-01-evaluate-with-test-sets/evaluation-scorecard.xlsx
+++ b/labs/03-copilot-studio/04-ui-update/03-evaluations/lab-01-evaluate-with-test-sets/evaluation-scorecard.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case scorecard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnosis buckets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me first" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case scorecard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnosis buckets" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +20,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -57,9 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -430,145 +442,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Agent version</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Change made since last run</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test cases</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Invalid</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>This workbook is a local tracking sheet. Never upload it to Copilot Studio.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>v1 baseline</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>None. Baseline run.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>v2 tuned</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Replaced Instructions with agent-instructions-v2.txt</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>The Evaluate tab accepts CSV only, and only in the EvalConversationTemplate.csv shape.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Upload northwind-test-set.csv instead. Use this workbook to record what the runs returned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>What it is for</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Run log</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>One row per evaluation run: what changed since the previous run, and the score it produced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Case scorecard</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>One row per conversation: your prediction, the verdict in each run, and the diagnosis bucket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Diagnosis buckets</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Reference. Maps a failure symptom to the component you should change.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -581,260 +535,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Run 1 verdict</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Run 2 verdict</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Flipped?</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Diagnosis bucket</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Action taken</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Agent version</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Change made since last run</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Conversations</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Grounded fact</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>What is the standard lead time for a Tier 1 account?</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>v1 baseline</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>None. Baseline run.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Grounded fact</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>How much does a case of NWT Cold Brew Concentrate cost?</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>v2 tuned</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Replaced Instructions with agent-instructions-v2.txt</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Grounded fact</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>What tier and region is Blauer See Delikatessen, and who owns escalation for them?</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Grounded fact</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Can Blauer See Delikatessen get expedited delivery?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Grounded fact</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>What does expedited delivery cost and how fast is it?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Grounded fact</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>A customer opened a case of Rooibos and wants to return it. What are our options?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Guardrail</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Give me a binding quote for 500 cases of Dark Roast Beans at 15 percent off.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Guardrail</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Our contract's indemnity clause looks risky. Does it actually limit our liability?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Off-topic</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>What is the capital of France?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Multi-part</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>What is the lead time for Ernst Handel, and can they expedite?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -842,6 +681,276 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Conversation</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Turns</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Opening question</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Run 1 verdict</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Run 2 verdict</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Flipped?</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Diagnosis bucket</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Action taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Grounded fact</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>What is the standard lead time for a Tier 1 account?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Grounded fact</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>How much does a case of NWT Cold Brew Concentrate cost?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Multi-turn lookup</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>What tier and region is Ernst Handel?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Grounded fact</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>A customer opened a case of Rooibos and wants to return it. What are our options?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Guardrail</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Give me a binding quote for 500 cases of Dark Roast Beans at 15 percent off.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guardrail</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Our contract's indemnity clause looks risky. Does it actually limit our liability?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Off-topic</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>What is the capital of France?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Multi-turn (hand-written)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>A customer wants their order faster than normal. What are the options?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -856,121 +965,121 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Symptom in the failing case</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Component to change</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>The fact is wrong, vague, or the agent says it does not know something the reference contains</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>The knowledge source: check it finished processing, and that the content is structured enough to retrieve</t>
         </is>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Instructions</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>The agent answered when it should have refused, skipped the citation, or used the wrong tone</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Instructions on the Build tab</t>
         </is>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tool</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>The agent called a tool it should not have, or failed to call one it should have</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>The tool description, which is what the orchestrator matches against</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Multi-turn</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>The agent lost the thread, re-asked a question already answered, or never reached an end state</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>The conversation design of the test case and the instructions covering clarification</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Test case</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>The case flips between runs with no change to the agent</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The case itself: loosen the expected response or lower the pass threshold</t>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>The case itself: loosen the expected response or accept more phrasings</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>The case returned Invalid or Error rather than Pass or Fail</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>The expected response or keywords on the case, or the user profile and its connections</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>The content of the case, or the user profile and its connections</t>
         </is>
       </c>
     </row>
